--- a/data-manipulation-scripts/sheets-cleanup/sheets/ RETROVISOR 10_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/ RETROVISOR 10_02.xlsx
@@ -28,67 +28,67 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>RR PAR RIIE BMW GS650 360 ROSCA RT0037</t>
+    <t>RETROVISOR PAR RIIE BMW GS650 360 ROSCA RT0037</t>
   </si>
   <si>
     <t>7908885008957</t>
   </si>
   <si>
-    <t>RR  RIIE BMW GS650 800 HASTE LONGA RT0039</t>
+    <t>RETROVISOR RIIE BMW GS650 800 HASTE LONGA RT0039</t>
   </si>
   <si>
     <t>06314430286858</t>
   </si>
   <si>
-    <t>RR IRON CG125 150 160 2014 A 2017 352396</t>
+    <t>RETROVISORIRON CG125 150 160 2014 A 2017 352396</t>
   </si>
   <si>
     <t>7898572844084</t>
   </si>
   <si>
-    <t>RR AWA FAZER150 2015 514</t>
+    <t>RETROVISOR AWA FAZER150 2015 514</t>
   </si>
   <si>
     <t>7899754900109</t>
   </si>
   <si>
-    <t>RR PAR EXTREMO CG TITAN FAN160cc 2014 002663</t>
+    <t>RETROVISORPAR EXTREMO CG TITAN FAN160cc 2014 002663</t>
   </si>
   <si>
     <t>7899754929971</t>
   </si>
   <si>
-    <t xml:space="preserve">RR EXTREMO FAZER YS150 2015/ NEO125/ NMAX </t>
+    <t xml:space="preserve">RETROVISOR EXTREMO FAZER YS150 2015/ NEO125/ NMAX </t>
   </si>
   <si>
     <t>7899754905180</t>
   </si>
   <si>
-    <t>RR PAR DAGOSTIN BIZ125/ BROS 2009 025451</t>
+    <t>RETROVISOR PAR DAGOSTIN BIZ125/ BROS 2009 025451</t>
   </si>
   <si>
     <t>7899754903100</t>
   </si>
   <si>
-    <t>RR DAGOSTIN TITAN KS/ES PAR 012299</t>
+    <t>RETROVISOR DAGOSTIN TITAN KS/ES PAR 012299</t>
   </si>
   <si>
     <t>7899754903742</t>
   </si>
   <si>
-    <t>RR EXTREMO BIZ125/ BROS 2009 015661</t>
+    <t>RETROVISOR EXTREMO BIZ125/ BROS 2009 015661</t>
   </si>
   <si>
-    <t>RR RIIE PAR MT03 07 09 ASTE LNGA ROSCA RT0035</t>
+    <t>RETROVISORRIIE PAR MT03 07 09 ASTE LNGA ROSCA RT0035</t>
   </si>
   <si>
-    <t>RR DMA PAR  MT03 07 09 ASTE LONGA ROSCA RT0035</t>
+    <t>RETROVISORDMA PAR  MT03 07 09 ASTE LONGA ROSCA RT0035</t>
   </si>
   <si>
     <t>7899624017463</t>
   </si>
   <si>
-    <t>RR MINI GVS FAZER YS150 PAR 4166</t>
+    <t>RETROVISOR MINI GVS FAZER YS150 PAR 4166</t>
   </si>
 </sst>
 </file>

--- a/data-manipulation-scripts/sheets-cleanup/sheets/ RETROVISOR 10_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/ RETROVISOR 10_02.xlsx
@@ -40,7 +40,7 @@
     <t>06314430286858</t>
   </si>
   <si>
-    <t>RETROVISORIRON CG125 150 160 2014 A 2017 352396</t>
+    <t>RETROVISOR IRON CG125 150 160 2014 A 2017 352396</t>
   </si>
   <si>
     <t>7898572844084</t>
@@ -52,7 +52,7 @@
     <t>7899754900109</t>
   </si>
   <si>
-    <t>RETROVISORPAR EXTREMO CG TITAN FAN160cc 2014 002663</t>
+    <t>RETROVISOR PAR EXTREMO CG TITAN FAN160cc 2014 002663</t>
   </si>
   <si>
     <t>7899754929971</t>
@@ -79,10 +79,10 @@
     <t>RETROVISOR EXTREMO BIZ125/ BROS 2009 015661</t>
   </si>
   <si>
-    <t>RETROVISORRIIE PAR MT03 07 09 ASTE LNGA ROSCA RT0035</t>
+    <t xml:space="preserve">RETROVISOR RIIE PAR MT03 07 09 ASTE LNGA ROSCA RT0035  </t>
   </si>
   <si>
-    <t>RETROVISORDMA PAR  MT03 07 09 ASTE LONGA ROSCA RT0035</t>
+    <t>RETROVISOR DMA PAR  MT03 07 09 ASTE LONGA ROSCA RT0035</t>
   </si>
   <si>
     <t>7899624017463</t>
@@ -139,9 +139,6 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -153,6 +150,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -521,7 +521,9 @@
       <c r="C4" s="3">
         <v>1.0</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2">
+        <v>27.0</v>
+      </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -533,7 +535,9 @@
       <c r="C5" s="3">
         <v>1.0</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="2">
+        <v>45.0</v>
+      </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="1" t="s">
@@ -545,7 +549,9 @@
       <c r="C6" s="3">
         <v>7.0</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="2">
+        <v>30.0</v>
+      </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="1" t="s">
@@ -557,7 +563,9 @@
       <c r="C7" s="3">
         <v>2.0</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="2">
+        <v>45.0</v>
+      </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="1" t="s">
@@ -569,7 +577,9 @@
       <c r="C8" s="3">
         <v>2.0</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="2">
+        <v>30.0</v>
+      </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="1" t="s">
@@ -581,7 +591,9 @@
       <c r="C9" s="3">
         <v>1.0</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="2">
+        <v>30.0</v>
+      </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="1" t="s">
@@ -593,7 +605,9 @@
       <c r="C10" s="3">
         <v>4.0</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="2">
+        <v>30.0</v>
+      </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="1" t="s">
@@ -605,38 +619,44 @@
       <c r="C11" s="3">
         <v>1.0</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="2">
+        <v>30.0</v>
+      </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="3">
         <v>1.0</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="2">
+        <v>45.0</v>
+      </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <v>1.0</v>
       </c>
-      <c r="D13" s="9"/>
+      <c r="D13" s="8">
+        <v>50.0</v>
+      </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="8"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="7"/>
       <c r="D14" s="9"/>
     </row>
     <row r="15">
